--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/27750332e5828b7f/שולחן העבודה/lyn_xml_validator_streamlit_v2/lyn_xml_validator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{7BEE02C9-DAD2-488B-9ECE-110FD122E3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{323FF458-B0A3-4E49-9A82-472EFE72C6B5}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="8_{7BEE02C9-DAD2-488B-9ECE-110FD122E3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B34A4FD1-CEDB-4E74-889F-E72E0E308D7A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$178</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="588">
   <si>
     <t>מספר ח.פ</t>
   </si>
@@ -1791,6 +1791,15 @@
   </si>
   <si>
     <t xml:space="preserve">מנורה מבטחים ביטוח </t>
+  </si>
+  <si>
+    <t>פנסיה ריבית פיגורים</t>
+  </si>
+  <si>
+    <t>השתלמות ריבית פיגורים</t>
+  </si>
+  <si>
+    <t>גמל ריבית פיגורים</t>
   </si>
 </sst>
 </file>
@@ -2179,7 +2188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J175"/>
+  <dimension ref="A1:J178"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
@@ -2249,7 +2258,7 @@
         <v>126</v>
       </c>
       <c r="I2">
-        <v>120103</v>
+        <v>480228</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -5268,7 +5277,7 @@
         <v>600</v>
       </c>
       <c r="I97">
-        <v>678680</v>
+        <v>669436</v>
       </c>
       <c r="J97" t="s">
         <v>394</v>
@@ -7770,8 +7779,59 @@
         <v>576</v>
       </c>
     </row>
+    <row r="176" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B176" t="s">
+        <v>411</v>
+      </c>
+      <c r="C176" t="s">
+        <v>585</v>
+      </c>
+      <c r="G176" s="3">
+        <v>20</v>
+      </c>
+      <c r="H176">
+        <v>461</v>
+      </c>
+      <c r="I176">
+        <v>626106</v>
+      </c>
+    </row>
+    <row r="177" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B177" t="s">
+        <v>411</v>
+      </c>
+      <c r="C177" t="s">
+        <v>586</v>
+      </c>
+      <c r="G177" s="3">
+        <v>20</v>
+      </c>
+      <c r="H177">
+        <v>932</v>
+      </c>
+      <c r="I177">
+        <v>260588</v>
+      </c>
+    </row>
+    <row r="178" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B178" t="s">
+        <v>411</v>
+      </c>
+      <c r="C178" t="s">
+        <v>587</v>
+      </c>
+      <c r="G178" s="3">
+        <v>20</v>
+      </c>
+      <c r="H178">
+        <v>932</v>
+      </c>
+      <c r="I178">
+        <v>260586</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J175" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J178" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/27750332e5828b7f/שולחן העבודה/lyn_xml_validator_streamlit_v2/lyn_xml_validator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="8_{7BEE02C9-DAD2-488B-9ECE-110FD122E3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B34A4FD1-CEDB-4E74-889F-E72E0E308D7A}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="8_{7BEE02C9-DAD2-488B-9ECE-110FD122E3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3184A37D-2649-4BC6-BF26-F37D95B2C472}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1899,6 +1899,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2252,10 +2256,10 @@
         <v>12</v>
       </c>
       <c r="G2" s="3">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="H2">
-        <v>126</v>
+        <v>600</v>
       </c>
       <c r="I2">
         <v>480228</v>
